--- a/analysis/statistics/wilcoxon_multiset_micro_f1.xlsx
+++ b/analysis/statistics/wilcoxon_multiset_micro_f1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,12 +424,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>base_model</t>
+          <t>metric</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>metric</t>
+          <t>baseline_base_model</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -454,60 +454,65 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>scenario_base_model</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>scenario_template</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>scenario_contrastive</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>scenario_constrained_decoding</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>scenario_segmentation</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>n_pairs</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>baseline_mean</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>scenario_mean</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>mean_diff_scenario_minus_baseline</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>wilcoxon_statistic</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>significant_at_0.05</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -521,12 +526,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>multiset_micro_f1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>multiset_micro_f1</t>
+          <t>t5-base</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -551,12 +556,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>paraphrase</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>paraphrase</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -566,35 +571,36 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>4</v>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="M2" t="n">
-        <v>0.6133829977006118</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6133829977006118</v>
+        <v>0.6168008310407948</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>0.5827489838483213</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0.03405184719247345</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>all paired differences are exactly zero</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -604,12 +610,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>multiset_micro_f1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>multiset_micro_f1</t>
+          <t>t5-base</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -634,46 +640,51 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>paraphrase</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>paraphrase</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>4</v>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="M3" t="n">
-        <v>0.6133829977006118</v>
+        <v>5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6184872304968758</v>
+        <v>0.6168008310407948</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005104232796264041</v>
+        <v>0.5839582632896159</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>-0.03284256775117889</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -683,12 +694,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>multiset_micro_f1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>multiset_micro_f1</t>
+          <t>t5-base</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -713,12 +724,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>paraphrase</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>paraphrase</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -728,31 +739,36 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>4</v>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="M4" t="n">
-        <v>0.6133829977006118</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6184872304968758</v>
+        <v>0.6168008310407948</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005104232796264041</v>
+        <v>0.5975812189851615</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>-0.01921961205563327</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -762,12 +778,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>multiset_micro_f1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>multiset_micro_f1</t>
+          <t>t5-base</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -792,46 +808,51 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>gen-scl-nat</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>paraphrase</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>4</v>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="M5" t="n">
-        <v>0.6133829977006118</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.606579808693295</v>
+        <v>0.6168008310407948</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.006803189007316801</v>
+        <v>0.5847190269177355</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>-0.03208180412305928</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -841,12 +862,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>multiset_micro_f1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>multiset_micro_f1</t>
+          <t>t5-base</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -871,14 +892,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>flan-t5-base</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>gen-scl-nat</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>no</t>
@@ -886,31 +907,36 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>4</v>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6133829977006118</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.606579808693295</v>
+        <v>0.6168008310407948</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.006803189007316801</v>
+        <v>0.5863740502636061</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>-0.03042678077718863</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -920,12 +946,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>multiset_micro_f1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>multiset_micro_f1</t>
+          <t>t5-base</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -950,46 +976,51 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>flan-t5-base</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>gen-scl-nat</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>4</v>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6133829977006118</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6077462017727236</v>
+        <v>0.6168008310407948</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.005636795927888127</v>
+        <v>0.5797283288997976</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>-0.03707250214099711</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -999,76 +1030,753 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>multiset_micro_f1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>flan-t5-base</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.6168008310407948</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5887107083770675</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.02809012266372723</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>multiset_micro_f1</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>paraphrase</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>flan-t5-base</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>gen-scl-nat</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.6133829977006118</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.6077462017727236</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-0.005636795927888127</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.6168008310407948</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.5767453463330888</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.04005548470770592</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>multiset_micro_f1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.6168008310407948</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.6141449158819898</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.002655915158804922</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>multiset_micro_f1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.6168008310407948</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.6112301889825577</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.005570642058237096</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>multiset_micro_f1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.6168008310407948</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.61641276117372</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.0003880698670747362</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>7</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>multiset_micro_f1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.6168008310407948</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.59179938677253</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.02500144426826478</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>multiset_micro_f1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.6168008310407948</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.5975248847321127</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.01927594630868201</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>multiset_micro_f1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>5</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.6168008310407948</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.6064082259568043</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.01039260508399042</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>multiset_micro_f1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>5</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.6168008310407948</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.607632487010589</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.009168344030205722</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
